--- a/New game/Assets/ArtRes/Excel/CardSynthesisFormulaInfo.xlsx
+++ b/New game/Assets/ArtRes/Excel/CardSynthesisFormulaInfo.xlsx
@@ -34,7 +34,7 @@
     <t>cardID</t>
   </si>
   <si>
-    <t>synthesize_to_ids</t>
+    <t>synthesizeCard</t>
   </si>
   <si>
     <t>resultResName</t>
